--- a/Excel/MineConfig.xlsx
+++ b/Excel/MineConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
@@ -35,28 +38,16 @@
     <t>Type</t>
   </si>
   <si>
+    <t>RequireLevel</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
     <t>Rate</t>
   </si>
   <si>
-    <t>StartRate</t>
-  </si>
-  <si>
-    <t>EndRate</t>
-  </si>
-  <si>
-    <t>AttrValue</t>
-  </si>
-  <si>
-    <t>RiseAttr</t>
-  </si>
-  <si>
-    <t>RisePower</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
+    <t>RiseRate</t>
   </si>
   <si>
     <t>Des</t>
@@ -68,9 +59,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>long</t>
-  </si>
-  <si>
     <t>铁矿</t>
   </si>
   <si>
@@ -201,6 +189,84 @@
   </si>
   <si>
     <t>减伤倍率</t>
+  </si>
+  <si>
+    <t>幸运石</t>
+  </si>
+  <si>
+    <t>幸运</t>
+  </si>
+  <si>
+    <t>白水晶</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>太阳石</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>泰坦石</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>物伤石</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>法伤石</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>道伤石</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>韧性石</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>破韧石</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>矿石之精</t>
+  </si>
+  <si>
+    <t>蓝矿等级+1%</t>
+  </si>
+  <si>
+    <t>宝石之精</t>
+  </si>
+  <si>
+    <t>紫矿等级+1%</t>
+  </si>
+  <si>
+    <t>水晶之心</t>
+  </si>
+  <si>
+    <t>橙矿等级+1%</t>
+  </si>
+  <si>
+    <t>异石之心</t>
+  </si>
+  <si>
+    <t>红矿等级+1%</t>
   </si>
 </sst>
 </file>
@@ -213,7 +279,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +297,12 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF05073B"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -703,142 +775,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1158,937 +1231,907 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M27"/>
+  <dimension ref="C1:I41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="11" width="12.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="1" customHeight="1" spans="3:9">
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:9">
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="H6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>10</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" ref="G7:G27" si="0">H6+1</f>
-        <v>10001</v>
+        <v>100000</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H27" si="1">H6+F7</f>
-        <v>20000</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>10</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>20001</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>10</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>30001</v>
+        <v>100000</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>10</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>15</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="1">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>40001</v>
+        <v>100000</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>50000</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>10</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>50001</v>
+        <v>1000</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="1"/>
-        <v>50100</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>500</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>15</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>50101</v>
+        <v>1000</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="1"/>
-        <v>50200</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>500</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
-        <v>50201</v>
+        <v>1000</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="1"/>
-        <v>50300</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+        <v>500</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>15</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>50301</v>
+        <v>1000</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="1"/>
-        <v>50400</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
+        <v>500</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:9">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>15</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>50401</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="1"/>
-        <v>50500</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:13">
+        <v>500</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:9">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>50501</v>
+        <v>1000</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="1"/>
-        <v>50600</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:13">
+        <v>500</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:9">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>50601</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="1"/>
-        <v>50610</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:9">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>50611</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="1"/>
-        <v>50620</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:9">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
-        <v>15</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>50621</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="1"/>
-        <v>50630</v>
-      </c>
-      <c r="I19" s="1">
-        <v>1</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:13">
+        <v>50</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:9">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>50631</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="1"/>
-        <v>50631</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
-        <v>100</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:13">
+        <v>10</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:9">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>50632</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="1"/>
-        <v>50632</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>100</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:13">
+        <v>10</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:9">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>50633</v>
+        <v>8</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="1"/>
-        <v>50633</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1">
-        <v>100</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:13">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:9">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="1">
         <v>15</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <f t="shared" si="0"/>
-        <v>50634</v>
-      </c>
       <c r="H23" s="1">
-        <f t="shared" si="1"/>
-        <v>50634</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>100</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:13">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:9">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="1">
         <v>15</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <f t="shared" si="0"/>
-        <v>50635</v>
-      </c>
       <c r="H24" s="1">
-        <f t="shared" si="1"/>
-        <v>50635</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>100</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:13">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:9">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1">
         <v>15</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <f t="shared" si="0"/>
-        <v>50636</v>
-      </c>
       <c r="H25" s="1">
-        <f t="shared" si="1"/>
-        <v>50636</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>100</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:13">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:9">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
-        <v>50637</v>
+        <v>10</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="1"/>
-        <v>50637</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>100</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:13">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:9">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:9">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>34</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="1">
+        <v>30</v>
+      </c>
+      <c r="H28" s="1">
+        <v>20</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:9">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>36</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="1">
+        <v>30</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:9">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>38</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="1">
+        <v>30</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:9">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>40</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="1">
         <v>15</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:9">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
         <v>1</v>
       </c>
-      <c r="G27" s="1">
-        <f t="shared" si="0"/>
-        <v>50638</v>
-      </c>
-      <c r="H27" s="1">
-        <f t="shared" si="1"/>
-        <v>50638</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="E32" s="1">
+        <v>50</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:9">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
         <v>1</v>
       </c>
-      <c r="J27" s="1">
+      <c r="E33" s="1">
+        <v>50</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" s="1">
+        <v>10</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:9">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
         <v>1</v>
       </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>57</v>
+      <c r="E34" s="1">
+        <v>50</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="1">
+        <v>10</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:9">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>60</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G35" s="1">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:9">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>70</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:9">
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:9">
+      <c r="C38" s="1">
+        <v>101</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="1">
+        <v>6</v>
+      </c>
+      <c r="H38" s="1">
+        <v>6</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:9">
+      <c r="C39" s="1">
+        <v>102</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="1">
+        <v>6</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:9">
+      <c r="C40" s="1">
+        <v>103</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>30</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" s="1">
+        <v>6</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:9">
+      <c r="C41" s="1">
+        <v>104</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>40</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="1">
+        <v>3</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 D4 D5 C4:C5 E4:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
